--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -877,7 +877,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -886,7 +886,7 @@
         <v>21</v>
       </c>
       <c r="I14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" s="13" t="s">
         <v>20</v>
@@ -895,7 +895,7 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
@@ -911,20 +911,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>2</v>
       </c>
       <c r="G15" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-60</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -949,35 +949,35 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
+        <v>2</v>
+      </c>
+      <c r="G16" s="14">
         <v>3</v>
       </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
         <v>7</v>
       </c>
       <c r="J16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K16" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-53.333333333333</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E17" s="15">
-        <v>-28.571428571428</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.285714285714</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I17" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J17" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="K17" s="15">
-        <v>-16.129032258064</v>
+        <v>-20</v>
       </c>
       <c r="L17" s="15">
-        <v>18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1034,32 +1034,32 @@
       <c r="C18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-50</v>
       </c>
       <c r="F18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
+        <v>-60</v>
+      </c>
+      <c r="I18" s="14">
+        <v>2</v>
+      </c>
+      <c r="J18" s="14">
+        <v>8</v>
+      </c>
+      <c r="K18" s="15">
         <v>-75</v>
       </c>
-      <c r="I18" s="14">
-        <v>1</v>
-      </c>
-      <c r="J18" s="14">
-        <v>6</v>
-      </c>
-      <c r="K18" s="15">
-        <v>-83.333333333333</v>
-      </c>
       <c r="L18" s="15">
-        <v>-80</v>
+        <v>-75</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>-25</v>
+        <v>250</v>
       </c>
       <c r="F19" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G19" s="14">
         <v>16</v>
       </c>
       <c r="H19" s="15">
-        <v>-31.25</v>
+        <v>-6.25</v>
       </c>
       <c r="I19" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J19" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K19" s="15">
-        <v>-25</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L19" s="15">
-        <v>-56.097560975609</v>
+        <v>-46.808510638297</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1114,34 +1114,34 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>75</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H20" s="15">
-        <v>-40</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I20" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J20" s="14">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>-48.148148148148</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.315789473684</v>
+        <v>-32</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E21" s="18">
-        <v>11.764705882352</v>
+        <v>40</v>
       </c>
       <c r="F21" s="17">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G21" s="17">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="H21" s="18">
-        <v>-31.428571428571</v>
+        <v>-17.1875</v>
       </c>
       <c r="I21" s="17">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="J21" s="17">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="K21" s="18">
-        <v>-30</v>
+        <v>-23.636363636363</v>
       </c>
       <c r="L21" s="18">
-        <v>-32.038834951456</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>10</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="F24" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G24" s="14">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H24" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="J24" s="14">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.517241379310</v>
+        <v>-15.492957746478</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.259259259259</v>
+        <v>-17.808219178082</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,34 +1319,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E25" s="15">
-        <v>133.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F25" s="14">
         <v>18</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>63.636363636363</v>
+        <v>38.461538461538</v>
       </c>
       <c r="I25" s="14">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J25" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K25" s="15">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="L25" s="15">
-        <v>162.5</v>
+        <v>188.888888888889</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>50</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>16</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="I26" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="J26" s="14">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="K26" s="15">
-        <v>18.181818181818</v>
+        <v>-2.272727272727</v>
       </c>
       <c r="L26" s="15">
-        <v>14.705882352941</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1413,22 +1413,22 @@
         <v>2</v>
       </c>
       <c r="G27" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-60</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>21</v>
+        <v>-57.142857142857</v>
+      </c>
+      <c r="L27" s="15">
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1444,20 +1444,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>1</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="14">
         <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="14">
         <v>1</v>
@@ -1482,8 +1482,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1501,7 +1501,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1523,8 +1523,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1533,7 +1533,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1542,7 +1542,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1636,7 +1636,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>
@@ -1645,7 +1645,7 @@
         <v>20</v>
       </c>
       <c r="J33" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -867,8 +867,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -917,14 +917,14 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>2</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>3</v>
@@ -949,35 +949,35 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" s="15">
         <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-58.823529411764</v>
+        <v>-60</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
         <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-10.526315789473</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="I17" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J17" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K17" s="15">
-        <v>-20</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="L17" s="15">
-        <v>0</v>
+        <v>-9.375</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1031,23 +1031,23 @@
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-50</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>-60</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
         <v>2</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>1</v>
+      </c>
+      <c r="D19" s="14">
         <v>7</v>
       </c>
-      <c r="D19" s="14">
-        <v>2</v>
-      </c>
       <c r="E19" s="15">
-        <v>250</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="F19" s="14">
         <v>15</v>
       </c>
       <c r="G19" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="15">
-        <v>-6.25</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I19" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J19" s="14">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.846153846153</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L19" s="15">
-        <v>-46.808510638297</v>
+        <v>-46</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1114,34 +1114,34 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G20" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-27.777777777777</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K20" s="15">
-        <v>-39.285714285714</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="L20" s="15">
-        <v>-32</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="D21" s="17">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E21" s="18">
-        <v>40</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="G21" s="17">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="H21" s="18">
-        <v>-17.1875</v>
+        <v>-22.950819672131</v>
       </c>
       <c r="I21" s="17">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="J21" s="17">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.636363636363</v>
+        <v>-26.229508196721</v>
       </c>
       <c r="L21" s="18">
-        <v>-33.333333333333</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>8</v>
+      </c>
+      <c r="D24" s="14">
         <v>10</v>
       </c>
-      <c r="D24" s="14">
-        <v>13</v>
-      </c>
       <c r="E24" s="15">
-        <v>-23.076923076923</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="14">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G24" s="14">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-2.564102564102</v>
       </c>
       <c r="I24" s="14">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J24" s="14">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.492957746478</v>
+        <v>-16.049382716049</v>
       </c>
       <c r="L24" s="15">
-        <v>-17.808219178082</v>
+        <v>-18.072289156626</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,34 +1319,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D25" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
         <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>38.461538461538</v>
+        <v>23.076923076923</v>
       </c>
       <c r="I25" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J25" s="14">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K25" s="15">
-        <v>30</v>
+        <v>21.739130434782</v>
       </c>
       <c r="L25" s="15">
-        <v>188.888888888889</v>
+        <v>154.545454545455</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>-63.636363636363</v>
+        <v>-12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="H26" s="15">
-        <v>-19.354838709677</v>
+        <v>-30.303030303030</v>
       </c>
       <c r="I26" s="14">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="J26" s="14">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="K26" s="15">
-        <v>-2.272727272727</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="L26" s="15">
-        <v>-6.521739130434</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1403,20 +1403,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>3</v>
@@ -1441,8 +1441,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1450,26 +1450,26 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="F28" s="14">
+        <v>1</v>
       </c>
       <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
+        <v>0</v>
+      </c>
+      <c r="I28" s="14">
         <v>2</v>
-      </c>
-      <c r="H28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="I28" s="14">
-        <v>1</v>
       </c>
       <c r="J28" s="14">
         <v>2</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1482,8 +1482,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1523,8 +1523,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1626,11 +1626,11 @@
       <c r="C33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D33" s="14">
-        <v>1</v>
-      </c>
-      <c r="E33" s="15">
-        <v>-100</v>
+      <c r="D33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -911,17 +911,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -930,10 +930,10 @@
         <v>3</v>
       </c>
       <c r="J15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -949,14 +949,14 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
@@ -971,10 +971,10 @@
         <v>8</v>
       </c>
       <c r="J16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L16" s="15">
         <v>-60</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-66.666666666666</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
         <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-31.578947368421</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="I17" s="14">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="J17" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K17" s="15">
-        <v>-23.684210526315</v>
+        <v>-23.255813953488</v>
       </c>
       <c r="L17" s="15">
-        <v>-9.375</v>
+        <v>-5.714285714285</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1031,35 +1031,35 @@
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K18" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-75</v>
+        <v>-70</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1076,10 +1076,10 @@
         <v>1</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-85.714285714285</v>
+        <v>-75</v>
       </c>
       <c r="F19" s="14">
         <v>15</v>
@@ -1091,16 +1091,16 @@
         <v>-11.764705882352</v>
       </c>
       <c r="I19" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J19" s="14">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.181818181818</v>
+        <v>-18.918918918918</v>
       </c>
       <c r="L19" s="15">
-        <v>-46</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1114,34 +1114,34 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>-80</v>
       </c>
       <c r="F20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I20" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J20" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K20" s="15">
-        <v>-34.482758620689</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L20" s="15">
-        <v>-34.482758620689</v>
+        <v>-35.483870967741</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-58.333333333333</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F21" s="17">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.950819672131</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I21" s="17">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="J21" s="17">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="K21" s="18">
-        <v>-26.229508196721</v>
+        <v>-28.776978417266</v>
       </c>
       <c r="L21" s="18">
-        <v>-35.714285714285</v>
+        <v>-34.437086092715</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E24" s="15">
-        <v>-20</v>
+        <v>25</v>
       </c>
       <c r="F24" s="14">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G24" s="14">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H24" s="15">
-        <v>-2.564102564102</v>
+        <v>-5.405405405405</v>
       </c>
       <c r="I24" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="J24" s="14">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.049382716049</v>
+        <v>-14.117647058823</v>
       </c>
       <c r="L24" s="15">
-        <v>-18.072289156626</v>
+        <v>-23.157894736842</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1318,23 +1318,23 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>2</v>
-      </c>
-      <c r="D25" s="14">
-        <v>3</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-33.333333333333</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H25" s="15">
-        <v>23.076923076923</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I25" s="14">
         <v>28</v>
@@ -1346,7 +1346,7 @@
         <v>21.739130434782</v>
       </c>
       <c r="L25" s="15">
-        <v>154.545454545455</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1363,31 +1363,31 @@
         <v>7</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H26" s="15">
-        <v>-30.303030303030</v>
+        <v>-20</v>
       </c>
       <c r="I26" s="14">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="J26" s="14">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.846153846153</v>
+        <v>-3.389830508474</v>
       </c>
       <c r="L26" s="15">
-        <v>-3.846153846153</v>
+        <v>-8.064516129032</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1403,17 +1403,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
         <v>-100</v>
@@ -1422,10 +1422,10 @@
         <v>3</v>
       </c>
       <c r="J27" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K27" s="15">
-        <v>-57.142857142857</v>
+        <v>-62.5</v>
       </c>
       <c r="L27" s="15">
         <v>200</v>
@@ -1441,8 +1441,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1492,7 +1492,7 @@
         <v>21</v>
       </c>
       <c r="F29" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1509,8 +1509,8 @@
       <c r="K29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+      <c r="L29" s="15">
+        <v>200</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1533,7 +1533,7 @@
         <v>21</v>
       </c>
       <c r="F30" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1550,8 +1550,8 @@
       <c r="K30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+      <c r="L30" s="15">
+        <v>200</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -877,7 +877,7 @@
         <v>21</v>
       </c>
       <c r="F14" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -908,35 +908,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
         <v>1</v>
       </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-57.142857142857</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
+        <v>-28.571428571428</v>
+      </c>
+      <c r="L15" s="15">
+        <v>400</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -949,35 +949,35 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="14">
+      <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="E16" s="15">
-        <v>-100</v>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
+        <v>2</v>
+      </c>
+      <c r="G16" s="14">
         <v>3</v>
       </c>
-      <c r="G16" s="14">
-        <v>4</v>
-      </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J16" s="14">
         <v>9</v>
       </c>
       <c r="K16" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="L16" s="15">
-        <v>-60</v>
+        <v>-55</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>150</v>
       </c>
       <c r="F17" s="14">
         <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>-36.842105263157</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I17" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J17" s="14">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K17" s="15">
-        <v>-23.255813953488</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.714285714285</v>
+        <v>-5</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1034,11 +1034,11 @@
       <c r="C18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>0</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>3</v>
@@ -1050,16 +1050,16 @@
         <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J18" s="14">
         <v>9</v>
       </c>
       <c r="K18" s="15">
-        <v>-66.666666666666</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="L18" s="15">
-        <v>-70</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>-11.764705882352</v>
+        <v>-5</v>
       </c>
       <c r="I19" s="14">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J19" s="14">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="K19" s="15">
-        <v>-18.918918918918</v>
+        <v>-15.909090909090</v>
       </c>
       <c r="L19" s="15">
-        <v>-44.444444444444</v>
+        <v>-36.206896551724</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1114,34 +1114,34 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-80</v>
+        <v>250</v>
       </c>
       <c r="F20" s="14">
         <v>13</v>
       </c>
       <c r="G20" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H20" s="15">
-        <v>18.181818181818</v>
+        <v>44.444444444444</v>
       </c>
       <c r="I20" s="14">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K20" s="15">
-        <v>-41.176470588235</v>
+        <v>-25</v>
       </c>
       <c r="L20" s="15">
-        <v>-35.483870967741</v>
+        <v>-12.903225806451</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>-58.823529411764</v>
+        <v>109.090909090909</v>
       </c>
       <c r="F21" s="17">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G21" s="17">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.285714285714</v>
+        <v>4</v>
       </c>
       <c r="I21" s="17">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="J21" s="17">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="K21" s="18">
-        <v>-28.776978417266</v>
+        <v>-18.666666666666</v>
       </c>
       <c r="L21" s="18">
-        <v>-34.437086092715</v>
+        <v>-24.691358024691</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>25</v>
+        <v>44.444444444444</v>
       </c>
       <c r="F24" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G24" s="14">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H24" s="15">
-        <v>-5.405405405405</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="J24" s="14">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.117647058823</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="L24" s="15">
-        <v>-23.157894736842</v>
+        <v>-21.818181818181</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1318,35 +1318,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="C25" s="14">
+        <v>4</v>
+      </c>
+      <c r="D25" s="14">
+        <v>2</v>
+      </c>
+      <c r="E25" s="15">
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
+        <v>32</v>
+      </c>
+      <c r="J25" s="14">
+        <v>25</v>
+      </c>
+      <c r="K25" s="15">
         <v>28</v>
       </c>
-      <c r="J25" s="14">
-        <v>23</v>
-      </c>
-      <c r="K25" s="15">
-        <v>21.739130434782</v>
-      </c>
       <c r="L25" s="15">
-        <v>133.333333333333</v>
+        <v>128.571428571429</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
+        <v>22.222222222222</v>
+      </c>
+      <c r="F26" s="14">
+        <v>29</v>
+      </c>
+      <c r="G26" s="14">
+        <v>35</v>
+      </c>
+      <c r="H26" s="15">
+        <v>-17.142857142857</v>
+      </c>
+      <c r="I26" s="14">
+        <v>68</v>
+      </c>
+      <c r="J26" s="14">
+        <v>68</v>
+      </c>
+      <c r="K26" s="15">
         <v>0</v>
       </c>
-      <c r="F26" s="14">
-        <v>24</v>
-      </c>
-      <c r="G26" s="14">
-        <v>30</v>
-      </c>
-      <c r="H26" s="15">
-        <v>-20</v>
-      </c>
-      <c r="I26" s="14">
-        <v>57</v>
-      </c>
-      <c r="J26" s="14">
-        <v>59</v>
-      </c>
-      <c r="K26" s="15">
-        <v>-3.389830508474</v>
-      </c>
       <c r="L26" s="15">
-        <v>-8.064516129032</v>
+        <v>-17.073170731707</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1400,35 +1400,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+        <v>100</v>
+      </c>
+      <c r="F27" s="14">
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-62.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1453,11 +1453,11 @@
       <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="G28" s="14">
-        <v>1</v>
-      </c>
-      <c r="H28" s="15">
-        <v>0</v>
+      <c r="G28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I28" s="14">
         <v>2</v>
@@ -1469,7 +1469,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1636,7 +1636,7 @@
         <v>20</v>
       </c>
       <c r="G33" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H33" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -711,7 +711,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -876,8 +876,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -909,7 +909,7 @@
         <v>22</v>
       </c>
       <c r="C15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -918,25 +918,25 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J15" s="14">
         <v>7</v>
       </c>
       <c r="K15" s="15">
-        <v>-28.571428571428</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L15" s="15">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -959,25 +959,25 @@
         <v>21</v>
       </c>
       <c r="F16" s="14">
+        <v>3</v>
+      </c>
+      <c r="G16" s="14">
         <v>2</v>
       </c>
-      <c r="G16" s="14">
-        <v>3</v>
-      </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J16" s="14">
         <v>9</v>
       </c>
       <c r="K16" s="15">
-        <v>0</v>
+        <v>11.111111111111</v>
       </c>
       <c r="L16" s="15">
-        <v>-55</v>
+        <v>-50</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>4</v>
+      </c>
+      <c r="D17" s="14">
         <v>5</v>
       </c>
-      <c r="D17" s="14">
-        <v>2</v>
-      </c>
       <c r="E17" s="15">
-        <v>150</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>-14.285714285714</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J17" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K17" s="15">
-        <v>-15.555555555555</v>
+        <v>-14</v>
       </c>
       <c r="L17" s="15">
-        <v>-5</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1031,20 +1031,20 @@
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>1</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="E18" s="15">
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" s="15">
         <v>0</v>
@@ -1053,13 +1053,13 @@
         <v>4</v>
       </c>
       <c r="J18" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K18" s="15">
-        <v>-55.555555555555</v>
+        <v>-60</v>
       </c>
       <c r="L18" s="15">
-        <v>-63.636363636363</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
+        <v>233.333333333333</v>
+      </c>
+      <c r="F19" s="14">
+        <v>20</v>
+      </c>
+      <c r="G19" s="14">
+        <v>21</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-4.761904761904</v>
+      </c>
+      <c r="I19" s="14">
+        <v>47</v>
+      </c>
+      <c r="J19" s="14">
+        <v>47</v>
+      </c>
+      <c r="K19" s="15">
         <v>0</v>
       </c>
-      <c r="F19" s="14">
-        <v>19</v>
-      </c>
-      <c r="G19" s="14">
-        <v>20</v>
-      </c>
-      <c r="H19" s="15">
-        <v>-5</v>
-      </c>
-      <c r="I19" s="14">
-        <v>37</v>
-      </c>
-      <c r="J19" s="14">
-        <v>44</v>
-      </c>
-      <c r="K19" s="15">
-        <v>-15.909090909090</v>
-      </c>
       <c r="L19" s="15">
-        <v>-36.206896551724</v>
+        <v>-27.692307692307</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1113,32 +1113,32 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>7</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E20" s="15">
-        <v>250</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G20" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H20" s="15">
-        <v>44.444444444444</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I20" s="14">
         <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K20" s="15">
-        <v>-25</v>
+        <v>-32.5</v>
       </c>
       <c r="L20" s="15">
         <v>-12.903225806451</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>109.090909090909</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F21" s="17">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G21" s="17">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="H21" s="18">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="J21" s="17">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.666666666666</v>
+        <v>-14.723926380368</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.691358024691</v>
+        <v>-21.468926553672</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E24" s="15">
-        <v>44.444444444444</v>
+        <v>70</v>
       </c>
       <c r="F24" s="14">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G24" s="14">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="H24" s="15">
+        <v>36.363636363636</v>
+      </c>
+      <c r="I24" s="14">
+        <v>104</v>
+      </c>
+      <c r="J24" s="14">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15">
         <v>0</v>
       </c>
-      <c r="I24" s="14">
-        <v>86</v>
-      </c>
-      <c r="J24" s="14">
-        <v>94</v>
-      </c>
-      <c r="K24" s="15">
-        <v>-8.510638297872</v>
-      </c>
       <c r="L24" s="15">
-        <v>-21.818181818181</v>
+        <v>-14.049586776859</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,34 +1319,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
-      </c>
-      <c r="D25" s="14">
-        <v>2</v>
-      </c>
-      <c r="E25" s="15">
-        <v>100</v>
+        <v>5</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
         <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="I25" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="J25" s="14">
         <v>25</v>
       </c>
       <c r="K25" s="15">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L25" s="15">
-        <v>128.571428571429</v>
+        <v>117.647058823529</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="F26" s="14">
+        <v>31</v>
+      </c>
+      <c r="G26" s="14">
         <v>29</v>
       </c>
-      <c r="G26" s="14">
-        <v>35</v>
-      </c>
       <c r="H26" s="15">
-        <v>-17.142857142857</v>
+        <v>6.896551724137</v>
       </c>
       <c r="I26" s="14">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="J26" s="14">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>1.369863013698</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.073170731707</v>
+        <v>-22.916666666666</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1401,34 +1401,34 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
+        <v>1</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>3</v>
+      </c>
+      <c r="G27" s="14">
         <v>2</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>2</v>
-      </c>
-      <c r="G27" s="14">
-        <v>3</v>
-      </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="I27" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J27" s="14">
         <v>9</v>
       </c>
       <c r="K27" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L27" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1491,8 +1491,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="14">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1532,8 +1532,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="14">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1635,11 +1635,11 @@
       <c r="F33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G33" s="14">
-        <v>1</v>
-      </c>
-      <c r="H33" s="15">
-        <v>-100</v>
+      <c r="G33" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -895,7 +895,7 @@
         <v>21</v>
       </c>
       <c r="L14" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M14" s="13" t="s">
         <v>21</v>
@@ -908,32 +908,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="14">
         <v>1</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
       <c r="G15" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K15" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="L15" s="15">
         <v>500</v>
@@ -952,11 +952,11 @@
       <c r="C16" s="14">
         <v>1</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
       </c>
       <c r="F16" s="14">
         <v>3</v>
@@ -968,16 +968,16 @@
         <v>50</v>
       </c>
       <c r="I16" s="14">
+        <v>11</v>
+      </c>
+      <c r="J16" s="14">
         <v>10</v>
       </c>
-      <c r="J16" s="14">
-        <v>9</v>
-      </c>
       <c r="K16" s="15">
-        <v>11.111111111111</v>
+        <v>10</v>
       </c>
       <c r="L16" s="15">
-        <v>-50</v>
+        <v>-45</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>3</v>
+      </c>
+      <c r="D17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="14">
-        <v>5</v>
-      </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="I17" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J17" s="14">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K17" s="15">
-        <v>-14</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="L17" s="15">
-        <v>-8.510638297872</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1035,7 +1035,7 @@
         <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
         <v>-100</v>
@@ -1044,22 +1044,22 @@
         <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-60</v>
       </c>
       <c r="I18" s="14">
         <v>4</v>
       </c>
       <c r="J18" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K18" s="15">
-        <v>-60</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="L18" s="15">
-        <v>-66.666666666666</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>233.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>-4.761904761904</v>
+        <v>5</v>
       </c>
       <c r="I19" s="14">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="J19" s="14">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="L19" s="15">
-        <v>-27.692307692307</v>
+        <v>-23.880597014925</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1117,31 +1117,31 @@
         <v>20</v>
       </c>
       <c r="D20" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
         <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>-16.666666666666</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I20" s="14">
         <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="K20" s="15">
-        <v>-32.5</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L20" s="15">
-        <v>-12.903225806451</v>
+        <v>-22.857142857142</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>23.076923076923</v>
+        <v>-52.941176470588</v>
       </c>
       <c r="F21" s="17">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G21" s="17">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I21" s="17">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="J21" s="17">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.723926380368</v>
+        <v>-18.333333333333</v>
       </c>
       <c r="L21" s="18">
-        <v>-21.468926553672</v>
+        <v>-22.631578947368</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>70</v>
+        <v>12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G24" s="14">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H24" s="15">
-        <v>36.363636363636</v>
+        <v>41.935483870967</v>
       </c>
       <c r="I24" s="14">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="J24" s="14">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="K24" s="15">
         <v>0</v>
       </c>
       <c r="L24" s="15">
-        <v>-14.049586776859</v>
+        <v>-20</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,34 +1319,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>5</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+        <v>6</v>
+      </c>
+      <c r="D25" s="14">
+        <v>2</v>
+      </c>
+      <c r="E25" s="15">
+        <v>200</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G25" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H25" s="15">
-        <v>120</v>
+        <v>275</v>
       </c>
       <c r="I25" s="14">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J25" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K25" s="15">
-        <v>48</v>
+        <v>59.259259259259</v>
       </c>
       <c r="L25" s="15">
-        <v>117.647058823529</v>
+        <v>79.166666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
         <v>5</v>
       </c>
       <c r="E26" s="15">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="H26" s="15">
-        <v>6.896551724137</v>
+        <v>26.923076923076</v>
       </c>
       <c r="I26" s="14">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="J26" s="14">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K26" s="15">
-        <v>1.369863013698</v>
+        <v>6.410256410256</v>
       </c>
       <c r="L26" s="15">
-        <v>-22.916666666666</v>
+        <v>-17</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1400,35 +1400,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="14">
         <v>1</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
       <c r="G27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="14">
         <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K27" s="15">
-        <v>-33.333333333333</v>
+        <v>-40</v>
       </c>
       <c r="L27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1441,8 +1441,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1460,16 +1460,16 @@
         <v>21</v>
       </c>
       <c r="I28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J28" s="14">
         <v>2</v>
       </c>
       <c r="K28" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -711,7 +711,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -930,10 +930,10 @@
         <v>6</v>
       </c>
       <c r="J15" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L15" s="15">
         <v>500</v>
@@ -959,25 +959,25 @@
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
         <v>2</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I16" s="14">
+        <v>12</v>
+      </c>
+      <c r="J16" s="14">
         <v>11</v>
       </c>
-      <c r="J16" s="14">
-        <v>10</v>
-      </c>
       <c r="K16" s="15">
-        <v>10</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L16" s="15">
-        <v>-45</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
+        <v>22</v>
+      </c>
+      <c r="G17" s="14">
         <v>17</v>
       </c>
-      <c r="G17" s="14">
-        <v>16</v>
-      </c>
       <c r="H17" s="15">
-        <v>6.25</v>
+        <v>29.411764705882</v>
       </c>
       <c r="I17" s="14">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="J17" s="14">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K17" s="15">
-        <v>-14.814814814814</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="L17" s="15">
-        <v>-11.538461538461</v>
+        <v>-1.785714285714</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1031,35 +1031,35 @@
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="14">
-        <v>3</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
         <v>2</v>
       </c>
       <c r="G18" s="14">
+        <v>4</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-50</v>
+      </c>
+      <c r="I18" s="14">
         <v>5</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-60</v>
-      </c>
-      <c r="I18" s="14">
-        <v>4</v>
       </c>
       <c r="J18" s="14">
         <v>13</v>
       </c>
       <c r="K18" s="15">
-        <v>-69.230769230769</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="L18" s="15">
-        <v>-69.230769230769</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>5</v>
+      </c>
+      <c r="D19" s="14">
         <v>4</v>
       </c>
-      <c r="D19" s="14">
-        <v>6</v>
-      </c>
       <c r="E19" s="15">
-        <v>-33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
         <v>20</v>
       </c>
       <c r="H19" s="15">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I19" s="14">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="J19" s="14">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.773584905660</v>
+        <v>-1.754385964912</v>
       </c>
       <c r="L19" s="15">
-        <v>-23.880597014925</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1113,35 +1113,35 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>4</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G20" s="14">
         <v>13</v>
       </c>
       <c r="H20" s="15">
-        <v>-38.461538461538</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="I20" s="14">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J20" s="14">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="K20" s="15">
-        <v>-35.714285714285</v>
+        <v>-34.042553191489</v>
       </c>
       <c r="L20" s="15">
-        <v>-22.857142857142</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D21" s="17">
         <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-52.941176470588</v>
+        <v>17.647058823529</v>
       </c>
       <c r="F21" s="17">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="G21" s="17">
         <v>58</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.896551724137</v>
+        <v>15.517241379310</v>
       </c>
       <c r="I21" s="17">
-        <v>147</v>
+        <v>167</v>
       </c>
       <c r="J21" s="17">
-        <v>180</v>
+        <v>197</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.333333333333</v>
+        <v>-15.228426395939</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.631578947368</v>
+        <v>-18.137254901960</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D24" s="14">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>12.5</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F24" s="14">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G24" s="14">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="H24" s="15">
-        <v>41.935483870967</v>
+        <v>13.157894736842</v>
       </c>
       <c r="I24" s="14">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="J24" s="14">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K24" s="15">
-        <v>0</v>
+        <v>-5.691056910569</v>
       </c>
       <c r="L24" s="15">
-        <v>-20</v>
+        <v>-22.147651006711</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,34 +1319,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
       </c>
       <c r="E25" s="15">
+        <v>50</v>
+      </c>
+      <c r="F25" s="14">
+        <v>18</v>
+      </c>
+      <c r="G25" s="14">
+        <v>6</v>
+      </c>
+      <c r="H25" s="15">
         <v>200</v>
       </c>
-      <c r="F25" s="14">
-        <v>15</v>
-      </c>
-      <c r="G25" s="14">
-        <v>4</v>
-      </c>
-      <c r="H25" s="15">
-        <v>275</v>
-      </c>
       <c r="I25" s="14">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J25" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K25" s="15">
-        <v>59.259259259259</v>
+        <v>58.620689655172</v>
       </c>
       <c r="L25" s="15">
-        <v>79.166666666666</v>
+        <v>84</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D26" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>80</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F26" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H26" s="15">
-        <v>26.923076923076</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="J26" s="14">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="K26" s="15">
-        <v>6.410256410256</v>
+        <v>-3.370786516853</v>
       </c>
       <c r="L26" s="15">
-        <v>-17</v>
+        <v>-17.307692307692</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1422,13 +1422,13 @@
         <v>6</v>
       </c>
       <c r="J27" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K27" s="15">
-        <v>-40</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="L27" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1441,8 +1441,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -908,35 +908,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>1</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F15" s="14">
+        <v>2</v>
+      </c>
+      <c r="G15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="14">
-        <v>2</v>
-      </c>
       <c r="H15" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K15" s="15">
-        <v>-33.333333333333</v>
+        <v>-30</v>
       </c>
       <c r="L15" s="15">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -950,34 +950,34 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
+        <v>6</v>
+      </c>
+      <c r="G16" s="14">
         <v>4</v>
       </c>
-      <c r="G16" s="14">
-        <v>2</v>
-      </c>
       <c r="H16" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K16" s="15">
-        <v>9.090909090909</v>
+        <v>15.384615384615</v>
       </c>
       <c r="L16" s="15">
-        <v>-45.454545454545</v>
+        <v>-37.5</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F17" s="14">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
         <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>29.411764705882</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="J17" s="14">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K17" s="15">
-        <v>-8.333333333333</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="L17" s="15">
-        <v>-1.785714285714</v>
+        <v>-1.754385964912</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1050,16 +1050,16 @@
         <v>-50</v>
       </c>
       <c r="I18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J18" s="14">
         <v>13</v>
       </c>
       <c r="K18" s="15">
-        <v>-61.538461538461</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L18" s="15">
-        <v>-64.285714285714</v>
+        <v>-62.5</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E19" s="15">
-        <v>25</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F19" s="14">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G19" s="14">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>25</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J19" s="14">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="K19" s="15">
-        <v>-1.754385964912</v>
+        <v>-10.294117647058</v>
       </c>
       <c r="L19" s="15">
-        <v>-22.222222222222</v>
+        <v>-19.736842105263</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1114,34 +1114,34 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>-20</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="G20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H20" s="15">
-        <v>-15.384615384615</v>
+        <v>-78.571428571428</v>
       </c>
       <c r="I20" s="14">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J20" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K20" s="15">
-        <v>-34.042553191489</v>
+        <v>-40</v>
       </c>
       <c r="L20" s="15">
-        <v>-16.216216216216</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E21" s="18">
-        <v>17.647058823529</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="F21" s="17">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="G21" s="17">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>15.517241379310</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="I21" s="17">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="J21" s="17">
-        <v>197</v>
+        <v>216</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.228426395939</v>
+        <v>-18.055555555555</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.137254901960</v>
+        <v>-18.807339449541</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D24" s="14">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>-63.636363636363</v>
+        <v>22.222222222222</v>
       </c>
       <c r="F24" s="14">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G24" s="14">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="H24" s="15">
-        <v>13.157894736842</v>
+        <v>8.510638297872</v>
       </c>
       <c r="I24" s="14">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="J24" s="14">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="K24" s="15">
-        <v>-5.691056910569</v>
+        <v>-2.127659574468</v>
       </c>
       <c r="L24" s="15">
-        <v>-22.147651006711</v>
+        <v>-15.853658536585</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1318,35 +1318,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>3</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
         <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>200</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I25" s="14">
         <v>46</v>
       </c>
       <c r="J25" s="14">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="K25" s="15">
-        <v>58.620689655172</v>
+        <v>48.387096774193</v>
       </c>
       <c r="L25" s="15">
-        <v>84</v>
+        <v>43.75</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E26" s="15">
-        <v>-72.727272727272</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.333333333333</v>
+        <v>3.703703703703</v>
       </c>
       <c r="I26" s="14">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="J26" s="14">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.370786516853</v>
+        <v>0</v>
       </c>
       <c r="L26" s="15">
-        <v>-17.307692307692</v>
+        <v>-11.214953271028</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1400,35 +1400,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>1</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F27" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I27" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K27" s="15">
-        <v>-45.454545454545</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L27" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1510,7 +1510,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1551,7 +1551,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -908,35 +908,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="14">
         <v>1</v>
       </c>
       <c r="E15" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H15" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K15" s="15">
-        <v>-30</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="L15" s="15">
-        <v>600</v>
+        <v>133.333333333333</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -950,34 +950,34 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="F16" s="14">
         <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>15.384615384615</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L16" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G17" s="14">
         <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="I17" s="14">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J17" s="14">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.677419354838</v>
+        <v>-11.940298507462</v>
       </c>
       <c r="L17" s="15">
-        <v>-1.754385964912</v>
+        <v>-3.278688524590</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1041,25 +1041,25 @@
         <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J18" s="14">
         <v>13</v>
       </c>
       <c r="K18" s="15">
-        <v>-53.846153846153</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L18" s="15">
-        <v>-62.5</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>-72.727272727272</v>
+        <v>75</v>
       </c>
       <c r="F19" s="14">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-8.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I19" s="14">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J19" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.294117647058</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L19" s="15">
-        <v>-19.736842105263</v>
+        <v>-18.072289156626</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1114,34 +1114,34 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-78.571428571428</v>
+        <v>-62.5</v>
       </c>
       <c r="I20" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J20" s="14">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="K20" s="15">
-        <v>-40</v>
+        <v>-41.071428571428</v>
       </c>
       <c r="L20" s="15">
-        <v>-28.571428571428</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-52.631578947368</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
         <v>52</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="H21" s="18">
-        <v>-21.212121212121</v>
+        <v>-28.767123287671</v>
       </c>
       <c r="I21" s="17">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="J21" s="17">
-        <v>216</v>
+        <v>236</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.055555555555</v>
+        <v>-18.644067796610</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.807339449541</v>
+        <v>-18.297872340425</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="E24" s="15">
-        <v>22.222222222222</v>
+        <v>333.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="G24" s="14">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H24" s="15">
-        <v>8.510638297872</v>
+        <v>41.860465116279</v>
       </c>
       <c r="I24" s="14">
-        <v>138</v>
+        <v>164</v>
       </c>
       <c r="J24" s="14">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K24" s="15">
-        <v>-2.127659574468</v>
+        <v>11.564625850340</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.853658536585</v>
+        <v>-2.958579881656</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1318,35 +1318,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>1</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G25" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>133.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I25" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J25" s="14">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K25" s="15">
-        <v>48.387096774193</v>
+        <v>42.424242424242</v>
       </c>
       <c r="L25" s="15">
-        <v>43.75</v>
+        <v>46.875</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G26" s="14">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H26" s="15">
-        <v>3.703703703703</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I26" s="14">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J26" s="14">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="K26" s="15">
-        <v>0</v>
+        <v>1.010101010101</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.214953271028</v>
+        <v>-11.504424778761</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1400,35 +1400,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>1</v>
       </c>
       <c r="E27" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K27" s="15">
-        <v>-41.666666666666</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L27" s="15">
-        <v>75</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -911,20 +911,20 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="14">
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
@@ -949,35 +949,35 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-25</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I16" s="14">
         <v>16</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>-5.882352941176</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-36</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" s="15">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="F17" s="14">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J17" s="14">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.940298507462</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L17" s="15">
-        <v>-3.278688524590</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1031,8 +1031,8 @@
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1043,11 +1043,11 @@
       <c r="F18" s="14">
         <v>3</v>
       </c>
-      <c r="G18" s="14">
-        <v>3</v>
-      </c>
-      <c r="H18" s="15">
-        <v>0</v>
+      <c r="G18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I18" s="14">
         <v>7</v>
@@ -1059,7 +1059,7 @@
         <v>-46.153846153846</v>
       </c>
       <c r="L18" s="15">
-        <v>-58.823529411764</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="F19" s="14">
+        <v>17</v>
+      </c>
+      <c r="G19" s="14">
+        <v>22</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-22.727272727272</v>
+      </c>
+      <c r="I19" s="14">
+        <v>69</v>
+      </c>
+      <c r="J19" s="14">
         <v>75</v>
       </c>
-      <c r="F19" s="14">
-        <v>20</v>
-      </c>
-      <c r="G19" s="14">
-        <v>25</v>
-      </c>
-      <c r="H19" s="15">
-        <v>-20</v>
-      </c>
-      <c r="I19" s="14">
-        <v>68</v>
-      </c>
-      <c r="J19" s="14">
-        <v>72</v>
-      </c>
       <c r="K19" s="15">
-        <v>-5.555555555555</v>
+        <v>-8</v>
       </c>
       <c r="L19" s="15">
-        <v>-18.072289156626</v>
+        <v>-20.689655172413</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1114,34 +1114,34 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>-62.5</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="I20" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J20" s="14">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="K20" s="15">
-        <v>-41.071428571428</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="L20" s="15">
-        <v>-26.666666666666</v>
+        <v>-25.531914893617</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>-69.230769230769</v>
       </c>
       <c r="F21" s="17">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G21" s="17">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>-28.767123287671</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="I21" s="17">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J21" s="17">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.644067796610</v>
+        <v>-21.285140562249</v>
       </c>
       <c r="L21" s="18">
-        <v>-18.297872340425</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D24" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="15">
-        <v>333.333333333333</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="G24" s="14">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="H24" s="15">
-        <v>41.860465116279</v>
+        <v>45</v>
       </c>
       <c r="I24" s="14">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J24" s="14">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="K24" s="15">
-        <v>11.564625850340</v>
+        <v>11.842105263157</v>
       </c>
       <c r="L24" s="15">
-        <v>-2.958579881656</v>
+        <v>-8.602150537634</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1328,25 +1328,25 @@
         <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G25" s="14">
         <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>25</v>
+        <v>-37.5</v>
       </c>
       <c r="I25" s="14">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J25" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K25" s="15">
-        <v>42.424242424242</v>
+        <v>37.142857142857</v>
       </c>
       <c r="L25" s="15">
-        <v>46.875</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
         <v>4</v>
       </c>
       <c r="E26" s="15">
+        <v>100</v>
+      </c>
+      <c r="F26" s="14">
+        <v>26</v>
+      </c>
+      <c r="G26" s="14">
         <v>25</v>
       </c>
-      <c r="F26" s="14">
-        <v>27</v>
-      </c>
-      <c r="G26" s="14">
-        <v>26</v>
-      </c>
       <c r="H26" s="15">
-        <v>3.846153846153</v>
+        <v>4</v>
       </c>
       <c r="I26" s="14">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="J26" s="14">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K26" s="15">
-        <v>1.010101010101</v>
+        <v>4.854368932038</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.504424778761</v>
+        <v>-10.743801652892</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1422,10 +1422,10 @@
         <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K27" s="15">
-        <v>-46.153846153846</v>
+        <v>-50</v>
       </c>
       <c r="L27" s="15">
         <v>16.666666666666</v>
@@ -1450,8 +1450,8 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="14">
-        <v>1</v>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>20</v>
@@ -1469,7 +1469,7 @@
         <v>50</v>
       </c>
       <c r="L28" s="15">
-        <v>50</v>
+        <v>-25</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -921,10 +921,10 @@
         <v>1</v>
       </c>
       <c r="G15" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H15" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
@@ -949,35 +949,35 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
         <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-44.444444444444</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>-15.789473684210</v>
+        <v>-5</v>
       </c>
       <c r="L16" s="15">
-        <v>-36</v>
+        <v>-24</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="F17" s="14">
         <v>14</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I17" s="14">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="J17" s="14">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.764705882352</v>
+        <v>-8</v>
       </c>
       <c r="L17" s="15">
-        <v>-14.285714285714</v>
+        <v>-2.816901408450</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1034,32 +1034,32 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
-      </c>
-      <c r="G18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H18" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="G18" s="14">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15">
+        <v>100</v>
       </c>
       <c r="I18" s="14">
         <v>7</v>
       </c>
       <c r="J18" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="15">
-        <v>-46.153846153846</v>
+        <v>-50</v>
       </c>
       <c r="L18" s="15">
-        <v>-61.111111111111</v>
+        <v>-65</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="15">
-        <v>-66.666666666666</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>-22.727272727272</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="J19" s="14">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="K19" s="15">
-        <v>-8</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="L19" s="15">
-        <v>-20.689655172413</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1116,32 +1116,32 @@
       <c r="C20" s="14">
         <v>2</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
         <v>7</v>
       </c>
-      <c r="E20" s="15">
-        <v>-71.428571428571</v>
-      </c>
-      <c r="F20" s="14">
-        <v>8</v>
-      </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-61.904761904761</v>
+        <v>-56.25</v>
       </c>
       <c r="I20" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J20" s="14">
         <v>63</v>
       </c>
       <c r="K20" s="15">
-        <v>-44.444444444444</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L20" s="15">
-        <v>-25.531914893617</v>
+        <v>-23.404255319148</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>-69.230769230769</v>
+        <v>46.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="H21" s="18">
-        <v>-30.434782608695</v>
+        <v>-26.865671641791</v>
       </c>
       <c r="I21" s="17">
-        <v>196</v>
+        <v>218</v>
       </c>
       <c r="J21" s="17">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.285140562249</v>
+        <v>-17.424242424242</v>
       </c>
       <c r="L21" s="18">
-        <v>-22.222222222222</v>
+        <v>-15.503875968992</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D24" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>36.363636363636</v>
       </c>
       <c r="F24" s="14">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="G24" s="14">
         <v>40</v>
       </c>
       <c r="H24" s="15">
-        <v>45</v>
+        <v>72.5</v>
       </c>
       <c r="I24" s="14">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="J24" s="14">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="K24" s="15">
-        <v>11.842105263157</v>
+        <v>13.496932515337</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.602150537634</v>
+        <v>-4.639175257731</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,34 +1319,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
-      </c>
-      <c r="D25" s="14">
-        <v>2</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-50</v>
+        <v>9</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>-37.5</v>
+        <v>83.333333333333</v>
       </c>
       <c r="I25" s="14">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="J25" s="14">
         <v>35</v>
       </c>
       <c r="K25" s="15">
-        <v>37.142857142857</v>
+        <v>62.857142857142</v>
       </c>
       <c r="L25" s="15">
-        <v>33.333333333333</v>
+        <v>54.054054054054</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>100</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F26" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H26" s="15">
-        <v>4</v>
+        <v>21.739130434782</v>
       </c>
       <c r="I26" s="14">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="J26" s="14">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="K26" s="15">
-        <v>4.854368932038</v>
+        <v>0.892857142857</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.743801652892</v>
+        <v>-8.870967741935</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1403,20 +1403,20 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="14">
         <v>1</v>
       </c>
       <c r="G27" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H27" s="15">
-        <v>-75</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
@@ -1441,8 +1441,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1450,8 +1450,8 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="F28" s="14">
+        <v>1</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>20</v>
@@ -1460,16 +1460,16 @@
         <v>21</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
         <v>2</v>
       </c>
       <c r="K28" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1482,8 +1482,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1491,8 +1491,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1501,7 +1501,7 @@
         <v>21</v>
       </c>
       <c r="I29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J29" s="13" t="s">
         <v>20</v>
@@ -1510,7 +1510,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1523,8 +1523,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1532,8 +1532,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1542,7 +1542,7 @@
         <v>21</v>
       </c>
       <c r="I30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J30" s="13" t="s">
         <v>20</v>
@@ -1551,7 +1551,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -911,32 +911,32 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="D15" s="14">
+        <v>2</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>7</v>
       </c>
       <c r="J15" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K15" s="15">
-        <v>-36.363636363636</v>
+        <v>-46.153846153846</v>
       </c>
       <c r="L15" s="15">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -950,34 +950,34 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>-5</v>
+        <v>-4.761904761904</v>
       </c>
       <c r="L16" s="15">
-        <v>-24</v>
+        <v>-25.925925925925</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E17" s="15">
-        <v>28.571428571428</v>
+        <v>-72.727272727272</v>
       </c>
       <c r="F17" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="H17" s="15">
-        <v>-6.666666666666</v>
+        <v>-37.5</v>
       </c>
       <c r="I17" s="14">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J17" s="14">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="K17" s="15">
-        <v>-8</v>
+        <v>-17.441860465116</v>
       </c>
       <c r="L17" s="15">
-        <v>-2.816901408450</v>
+        <v>-5.333333333333</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1041,25 +1041,25 @@
         <v>-100</v>
       </c>
       <c r="F18" s="14">
+        <v>1</v>
+      </c>
+      <c r="G18" s="14">
         <v>2</v>
       </c>
-      <c r="G18" s="14">
-        <v>1</v>
-      </c>
       <c r="H18" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="I18" s="14">
         <v>7</v>
       </c>
       <c r="J18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K18" s="15">
-        <v>-50</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-65</v>
+        <v>-70.833333333333</v>
       </c>
       <c r="M18" s="13" t="s">
         <v>21</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="H19" s="15">
-        <v>-20.833333333333</v>
+        <v>5.882352941176</v>
       </c>
       <c r="I19" s="14">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J19" s="14">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="K19" s="15">
-        <v>-3.703703703703</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L19" s="15">
-        <v>-13.333333333333</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1113,35 +1113,35 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>8</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="H20" s="15">
-        <v>-56.25</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I20" s="14">
         <v>36</v>
       </c>
       <c r="J20" s="14">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="K20" s="15">
-        <v>-42.857142857142</v>
+        <v>-49.295774647887</v>
       </c>
       <c r="L20" s="15">
-        <v>-23.404255319148</v>
+        <v>-28</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="E21" s="18">
-        <v>46.666666666666</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F21" s="17">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G21" s="17">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.865671641791</v>
+        <v>-40</v>
       </c>
       <c r="I21" s="17">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="J21" s="17">
-        <v>264</v>
+        <v>291</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.424242424242</v>
+        <v>-23.367697594501</v>
       </c>
       <c r="L21" s="18">
-        <v>-15.503875968992</v>
+        <v>-19.202898550724</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>36.363636363636</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="14">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="G24" s="14">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H24" s="15">
-        <v>72.5</v>
+        <v>67.647058823529</v>
       </c>
       <c r="I24" s="14">
-        <v>185</v>
+        <v>195</v>
       </c>
       <c r="J24" s="14">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="K24" s="15">
-        <v>13.496932515337</v>
+        <v>11.428571428571</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.639175257731</v>
+        <v>-4.878048780487</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,34 +1319,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>9</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D25" s="14">
+        <v>2</v>
+      </c>
+      <c r="E25" s="15">
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
         <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>83.333333333333</v>
+        <v>116.666666666667</v>
       </c>
       <c r="I25" s="14">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="J25" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K25" s="15">
-        <v>62.857142857142</v>
+        <v>59.459459459459</v>
       </c>
       <c r="L25" s="15">
-        <v>54.054054054054</v>
+        <v>51.282051282051</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>-44.444444444444</v>
+        <v>-81.818181818181</v>
       </c>
       <c r="F26" s="14">
+        <v>21</v>
+      </c>
+      <c r="G26" s="14">
         <v>28</v>
       </c>
-      <c r="G26" s="14">
-        <v>23</v>
-      </c>
       <c r="H26" s="15">
-        <v>21.739130434782</v>
+        <v>-25</v>
       </c>
       <c r="I26" s="14">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="J26" s="14">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="K26" s="15">
-        <v>0.892857142857</v>
+        <v>-5.691056910569</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.870967741935</v>
+        <v>-14.074074074074</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1403,32 +1403,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="D27" s="14">
+        <v>2</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-66.666666666666</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
       </c>
       <c r="J27" s="14">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K27" s="15">
-        <v>-50</v>
+        <v>-56.25</v>
       </c>
       <c r="L27" s="15">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1442,7 +1442,7 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1451,7 +1451,7 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G28" s="13" t="s">
         <v>20</v>
@@ -1460,16 +1460,16 @@
         <v>21</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
         <v>2</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="L28" s="15">
-        <v>-33.333333333333</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1482,8 +1482,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1523,8 +1523,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-116pct.xlsx
+++ b/data/source/weekly/cs-en-us-116pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -908,35 +908,35 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
       </c>
       <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G15" s="14">
         <v>3</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I15" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J15" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K15" s="15">
-        <v>-46.153846153846</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L15" s="15">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="M15" s="13" t="s">
         <v>21</v>
@@ -950,34 +950,34 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>-37.5</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
         <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>-4.761904761904</v>
+        <v>4.761904761904</v>
       </c>
       <c r="L16" s="15">
-        <v>-25.925925925925</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>21</v>
@@ -991,34 +991,34 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D17" s="14">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>-72.727272727272</v>
+        <v>-25</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H17" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I17" s="14">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="J17" s="14">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="K17" s="15">
-        <v>-17.441860465116</v>
+        <v>-18.085106382978</v>
       </c>
       <c r="L17" s="15">
-        <v>-5.333333333333</v>
+        <v>-7.228915662650</v>
       </c>
       <c r="M17" s="13" t="s">
         <v>21</v>
@@ -1040,23 +1040,23 @@
       <c r="E18" s="15">
         <v>-100</v>
       </c>
-      <c r="F18" s="14">
-        <v>1</v>
+      <c r="F18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G18" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="I18" s="14">
         <v>7</v>
       </c>
       <c r="J18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>-53.333333333333</v>
+        <v>-56.25</v>
       </c>
       <c r="L18" s="15">
         <v>-70.833333333333</v>
@@ -1073,34 +1073,34 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>5</v>
+      </c>
+      <c r="D19" s="14">
         <v>2</v>
       </c>
-      <c r="D19" s="14">
-        <v>4</v>
-      </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>150</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G19" s="14">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H19" s="15">
-        <v>5.882352941176</v>
+        <v>6.666666666666</v>
       </c>
       <c r="I19" s="14">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J19" s="14">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.882352941176</v>
+        <v>-1.149425287356</v>
       </c>
       <c r="L19" s="15">
-        <v>-14.893617021276</v>
+        <v>-14</v>
       </c>
       <c r="M19" s="13" t="s">
         <v>21</v>
@@ -1113,35 +1113,35 @@
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="H20" s="15">
-        <v>-71.428571428571</v>
+        <v>-75</v>
       </c>
       <c r="I20" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J20" s="14">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K20" s="15">
-        <v>-49.295774647887</v>
+        <v>-48.611111111111</v>
       </c>
       <c r="L20" s="15">
-        <v>-28</v>
+        <v>-30.188679245283</v>
       </c>
       <c r="M20" s="13" t="s">
         <v>21</v>
@@ -1155,34 +1155,34 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D21" s="17">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-77.777777777777</v>
+        <v>23.076923076923</v>
       </c>
       <c r="F21" s="17">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="H21" s="18">
-        <v>-40</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="I21" s="17">
-        <v>223</v>
+        <v>240</v>
       </c>
       <c r="J21" s="17">
-        <v>291</v>
+        <v>304</v>
       </c>
       <c r="K21" s="18">
-        <v>-23.367697594501</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L21" s="18">
-        <v>-19.202898550724</v>
+        <v>-18.367346938775</v>
       </c>
       <c r="M21" s="19" t="s">
         <v>21</v>
@@ -1278,34 +1278,34 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F24" s="14">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G24" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H24" s="15">
-        <v>67.647058823529</v>
+        <v>17.142857142857</v>
       </c>
       <c r="I24" s="14">
-        <v>195</v>
+        <v>205</v>
       </c>
       <c r="J24" s="14">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="K24" s="15">
-        <v>11.428571428571</v>
+        <v>12.637362637362</v>
       </c>
       <c r="L24" s="15">
-        <v>-4.878048780487</v>
+        <v>-4.205607476635</v>
       </c>
       <c r="M24" s="13" t="s">
         <v>21</v>
@@ -1319,34 +1319,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
         <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G25" s="14">
         <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>116.666666666667</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I25" s="14">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="J25" s="14">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K25" s="15">
-        <v>59.459459459459</v>
+        <v>61.538461538461</v>
       </c>
       <c r="L25" s="15">
-        <v>51.282051282051</v>
+        <v>53.658536585365</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1360,34 +1360,34 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E26" s="15">
-        <v>-81.818181818181</v>
+        <v>-72.222222222222</v>
       </c>
       <c r="F26" s="14">
         <v>21</v>
       </c>
       <c r="G26" s="14">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="H26" s="15">
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="I26" s="14">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="J26" s="14">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.691056910569</v>
+        <v>-14.184397163120</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.074074074074</v>
+        <v>-16.551724137931</v>
       </c>
       <c r="M26" s="13" t="s">
         <v>21</v>
@@ -1400,35 +1400,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
       </c>
       <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
       </c>
       <c r="G27" s="14">
         <v>4</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="I27" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J27" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K27" s="15">
-        <v>-56.25</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="L27" s="15">
-        <v>0</v>
+        <v>28.571428571428</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1441,32 +1441,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
-      <c r="G28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H28" s="13" t="s">
-        <v>21</v>
+      <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
+        <v>300</v>
       </c>
       <c r="I28" s="14">
         <v>7</v>
       </c>
       <c r="J28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K28" s="15">
-        <v>250</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L28" s="15">
         <v>16.666666666666</v>
@@ -1510,7 +1510,7 @@
         <v>21</v>
       </c>
       <c r="L29" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M29" s="13" t="s">
         <v>21</v>
@@ -1551,7 +1551,7 @@
         <v>21</v>
       </c>
       <c r="L30" s="15">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M30" s="13" t="s">
         <v>21</v>
